--- a/DOCUMENTS/Choco_Latte_report.xlsx
+++ b/DOCUMENTS/Choco_Latte_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://digipen824.sharepoint.com/sites/TeamChocoLatte/Shared Documents/General/project_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3DF5517-60B5-459E-B15E-D4853860676C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E902CF4-B833-44F6-BABE-8DCFF31D3609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" firstSheet="1" activeTab="1" xr2:uid="{A89F0CA0-527A-4B26-99DD-E728F0C1D180}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" firstSheet="1" activeTab="2" xr2:uid="{A89F0CA0-527A-4B26-99DD-E728F0C1D180}"/>
   </bookViews>
   <sheets>
     <sheet name="Step1-Overview" sheetId="1" r:id="rId1"/>
@@ -412,7 +412,7 @@
     <t>Normal / boss wave indicator</t>
   </si>
   <si>
-    <t xml:space="preserve">Animation to alert player when enemy waves or boss is approaching </t>
+    <t xml:space="preserve">Visual cues to alert player when enemy waves or boss is approaching </t>
   </si>
   <si>
     <t>Player Heal</t>
@@ -479,7 +479,7 @@
     <t>Walking animation</t>
   </si>
   <si>
-    <t>Encompasses all walking animation of enemies, bosses and choco shooter</t>
+    <t>Encompasses all walking animation of enemies and choco shooter</t>
   </si>
   <si>
     <t>General UI elements design</t>
@@ -2460,7 +2460,7 @@
         <v>63</v>
       </c>
       <c r="E20" s="33">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F20" s="33">
         <v>9</v>
@@ -2634,7 +2634,7 @@
         <v>75</v>
       </c>
       <c r="E26" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="33">
         <v>9</v>
@@ -2663,7 +2663,7 @@
         <v>77</v>
       </c>
       <c r="E27" s="33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27" s="33">
         <v>9</v>
@@ -2692,7 +2692,7 @@
         <v>79</v>
       </c>
       <c r="E28" s="33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="33">
         <v>9</v>
@@ -2721,7 +2721,7 @@
         <v>81</v>
       </c>
       <c r="E29" s="33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F29" s="33">
         <v>10</v>
@@ -2866,7 +2866,7 @@
         <v>91</v>
       </c>
       <c r="E34" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="33">
         <v>10</v>
@@ -2924,7 +2924,7 @@
         <v>95</v>
       </c>
       <c r="E36" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="33">
         <v>10</v>
@@ -3011,7 +3011,7 @@
         <v>101</v>
       </c>
       <c r="E39" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" s="33">
         <v>10</v>
@@ -3185,7 +3185,7 @@
         <v>114</v>
       </c>
       <c r="E45" s="33">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F45" s="33">
         <v>11</v>
@@ -3301,7 +3301,7 @@
         <v>122</v>
       </c>
       <c r="E49" s="33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49" s="33">
         <v>12</v>
@@ -3330,7 +3330,7 @@
         <v>124</v>
       </c>
       <c r="E50" s="33">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F50" s="33">
         <v>12</v>
@@ -3359,7 +3359,7 @@
         <v>126</v>
       </c>
       <c r="E51" s="33">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F51" s="33">
         <v>12</v>
@@ -3388,7 +3388,7 @@
         <v>129</v>
       </c>
       <c r="E52" s="33">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F52" s="33">
         <v>12</v>
@@ -3417,7 +3417,7 @@
         <v>131</v>
       </c>
       <c r="E53" s="33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F53" s="33">
         <v>12</v>
@@ -3461,7 +3461,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="30">
+    <row r="55" spans="1:9">
       <c r="A55" s="33" t="s">
         <v>10</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>138</v>
       </c>
       <c r="E56" s="33">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F56" s="33">
         <v>12</v>
@@ -3513,7 +3513,7 @@
         <v>43</v>
       </c>
       <c r="H56" s="33" t="s">
-        <v>132</v>
+        <v>30</v>
       </c>
       <c r="I56" s="33" t="s">
         <v>31</v>
@@ -4333,19 +4333,19 @@
       </c>
       <c r="E9" s="18">
         <f>SUMIFS('Step2-Task Backlog'!E:E,'Step2-Task Backlog'!B:B,Priorities!A$2, 'Step2-Task Backlog'!G:G, 'Step3-Budgeting'!A9)</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="18">
         <f>SUMIFS('Step2-Task Backlog'!E:E,'Step2-Task Backlog'!B:B,Priorities!A$2,'Step2-Task Backlog'!H:H,TaskTypes!A$5, 'Step2-Task Backlog'!G:G, 'Step3-Budgeting'!A9)</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G9" s="18">
         <f>SUMIFS('Step2-Task Backlog'!E:E,'Step2-Task Backlog'!I:I,"Yes",'Step2-Task Backlog'!G:G,'Step3-Budgeting'!A9)</f>
-        <v>42</v>
+        <v>40.5</v>
       </c>
       <c r="H9" s="18">
         <f>SUMIFS('Step2-Task Backlog'!E:E,'Step2-Task Backlog'!I:I,"Yes",'Step2-Task Backlog'!G:G,'Step3-Budgeting'!A9,'Step2-Task Backlog'!H:H,TaskTypes!$A$5) + SUMIFS('Step2-Task Backlog'!E:E,'Step2-Task Backlog'!I:I,"Yes",'Step2-Task Backlog'!G:G,'Step3-Budgeting'!A9,'Step2-Task Backlog'!H:H,TaskTypes!$A$6)</f>
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4395,19 +4395,19 @@
       </c>
       <c r="E11" s="18">
         <f>SUMIFS('Step2-Task Backlog'!E:E,'Step2-Task Backlog'!B:B,Priorities!A$2, 'Step2-Task Backlog'!G:G, 'Step3-Budgeting'!A11)</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F11" s="18">
         <f>SUMIFS('Step2-Task Backlog'!E:E,'Step2-Task Backlog'!B:B,Priorities!A$2,'Step2-Task Backlog'!H:H,TaskTypes!A$5, 'Step2-Task Backlog'!G:G, 'Step3-Budgeting'!A11)</f>
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G11" s="18">
         <f>SUMIFS('Step2-Task Backlog'!E:E,'Step2-Task Backlog'!I:I,"Yes",'Step2-Task Backlog'!G:G,'Step3-Budgeting'!A11)</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H11" s="18">
         <f>SUMIFS('Step2-Task Backlog'!E:E,'Step2-Task Backlog'!I:I,"Yes",'Step2-Task Backlog'!G:G,'Step3-Budgeting'!A11,'Step2-Task Backlog'!H:H,TaskTypes!$A$5) + SUMIFS('Step2-Task Backlog'!E:E,'Step2-Task Backlog'!I:I,"Yes",'Step2-Task Backlog'!G:G,'Step3-Budgeting'!A11,'Step2-Task Backlog'!H:H,TaskTypes!$A$6)</f>
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -4424,19 +4424,19 @@
       </c>
       <c r="E12" s="18">
         <f t="shared" si="1"/>
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F12" s="18">
         <f t="shared" si="1"/>
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G12" s="18">
         <f t="shared" si="1"/>
-        <v>118</v>
+        <v>120.5</v>
       </c>
       <c r="H12" s="18">
         <f t="shared" si="1"/>
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -10898,6 +10898,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="906065da-3fa6-4c3b-ab91-8edba4cfce3a">
@@ -10908,23 +10917,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32400A2A-7D96-4334-9F04-F88FABD9032F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8DA46A-17E0-4FD4-A74B-346E786BC052}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE25CA7D-4DC9-42E6-BCE7-999A796643AF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE25CA7D-4DC9-42E6-BCE7-999A796643AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8DA46A-17E0-4FD4-A74B-346E786BC052}"/>
 </file>